--- a/nguoi-phu-trach.xlsx
+++ b/nguoi-phu-trach.xlsx
@@ -801,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43.140625" customWidth="1" style="19" min="1" max="1"/>
@@ -812,6 +812,7 @@
     <col width="36" customWidth="1" style="19" min="6" max="6"/>
     <col width="14.7109375" customWidth="1" style="19" min="7" max="7"/>
     <col width="20" customWidth="1" style="19" min="8" max="8"/>
+    <col width="14" customWidth="1" style="19" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,6 +856,11 @@
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="V1" s="26" t="inlineStr">
+        <is>
+          <t>K gốc tuyến</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="19">
       <c r="A2" t="inlineStr">
@@ -1202,6 +1208,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15.75" customHeight="1" s="19">
       <c r="A12" t="inlineStr">
         <is>
@@ -1653,6 +1660,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="15.75" customHeight="1" s="19">
       <c r="A25" t="inlineStr">
         <is>
@@ -2708,6 +2716,11 @@
           <t>BĐáy 1m, Bmặt 7m, H 2m</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>K5+285</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="19">
       <c r="A52" t="inlineStr">
@@ -2740,6 +2753,11 @@
           <t>BĐáy 1m, Bmặt 7m, H 2m</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>K5+285</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" t="inlineStr">
@@ -2772,6 +2790,11 @@
           <t>BĐáy 0.8m, Bmặt 6.4m, H 2m</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>K5+285</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="19">
       <c r="A54" t="inlineStr">
@@ -2802,6 +2825,11 @@
       <c r="F54" t="inlineStr">
         <is>
           <t>BĐáy 0.8m, Bmặt 6.4m, H 2m</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>K5+285</t>
         </is>
       </c>
     </row>
@@ -3765,6 +3793,52 @@
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Ghi chú: 1 kênh chia nhiều người phụ trách theo từng đoạn K khác nhau → lặp lại đúng tên kênh ở nhiều dòng, mỗi dòng 1 đoạn K + 1 người. Loại kênh / Kích thước mặt cắt / Lưu lượng chỉ cần điền 1 lần cho cả kênh, không bắt buộc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Hành lang bờ Tả - Sông Nhuệ (CT1 -&gt; T292.6)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>K19+500</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>K29+020</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>K19+500</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Hành lang bờ Hữu - Sông Nhuệ (CH1 -&gt; H317.1)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>K19+050</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>K29+400</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>K19+050</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12441,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Kênh Cầu Sắt - Mô Cam</t>
@@ -12390,7 +12463,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Kênh Cầu Sắt - Mô Cam</t>
@@ -12413,7 +12485,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Kênh Cầu Sắt - Mô Cam</t>
@@ -12436,7 +12507,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Kênh Cầu Sắt - Mô Cam</t>
@@ -12459,7 +12529,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Kênh Cầu Sắt - Mô Cam</t>
@@ -12482,7 +12551,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12505,7 +12573,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12528,7 +12595,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12551,7 +12617,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12574,7 +12639,6 @@
           <t>2cửa</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12597,7 +12661,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12620,7 +12683,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12643,7 +12705,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12666,7 +12727,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12689,7 +12749,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12712,7 +12771,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12735,7 +12793,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12758,7 +12815,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12781,7 +12837,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12804,7 +12859,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12827,7 +12881,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12850,7 +12903,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Kênh Ngọc Hồi</t>
@@ -12873,7 +12925,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Kênh Tiêu Liên Ninh</t>
@@ -12896,7 +12947,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Kênh Tiêu Liên Ninh</t>
@@ -12919,7 +12969,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -12942,7 +12991,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -12965,7 +13013,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -12988,7 +13035,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13011,7 +13057,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13034,7 +13079,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13057,7 +13101,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13080,7 +13123,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13103,7 +13145,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13126,7 +13167,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13149,7 +13189,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13172,7 +13211,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13195,7 +13233,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13218,7 +13255,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13241,7 +13277,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13264,7 +13299,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13287,7 +13321,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13310,7 +13343,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13333,7 +13365,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13356,7 +13387,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13379,7 +13409,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13402,7 +13431,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13425,7 +13453,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13448,7 +13475,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13471,7 +13497,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Kênh Tiêu Đại Áng</t>
@@ -13494,7 +13519,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13517,7 +13541,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13540,7 +13563,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13563,7 +13585,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13586,7 +13607,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13609,7 +13629,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13632,7 +13651,6 @@
           <t>4 cửa</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13655,7 +13673,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13678,7 +13695,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13701,7 +13717,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13724,7 +13739,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13747,7 +13761,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13770,7 +13783,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13793,7 +13805,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13816,7 +13827,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13839,7 +13849,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13862,7 +13871,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13885,7 +13893,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13908,7 +13915,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13931,7 +13937,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13954,7 +13959,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -13977,7 +13981,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14000,7 +14003,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14023,7 +14025,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14046,7 +14047,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14069,7 +14069,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14092,7 +14091,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14115,7 +14113,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14138,7 +14135,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14161,7 +14157,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14184,7 +14179,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14207,7 +14201,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14230,7 +14223,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14253,7 +14245,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14276,7 +14267,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14299,7 +14289,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14322,7 +14311,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14345,7 +14333,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14368,7 +14355,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14391,7 +14377,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14414,7 +14399,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14437,7 +14421,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14460,7 +14443,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Kênh tưới Hồng Vân</t>
@@ -14483,7 +14465,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Kênh Đại Thanh</t>
@@ -14506,7 +14487,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Kênh Đại Thanh</t>
@@ -14529,7 +14509,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Kênh Đại Thanh</t>
@@ -14552,7 +14531,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Kênh Đại Thanh</t>
@@ -14575,7 +14553,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Kênh Đại Thanh</t>
@@ -14598,7 +14575,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Kênh Đại Thanh</t>
@@ -14621,7 +14597,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>Tuyến Kênh Hữu Hòa</t>
@@ -14644,7 +14619,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Tuyến Kênh Hữu Hòa</t>
@@ -14667,7 +14641,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Tuyến Kênh Hữu Hòa</t>
@@ -14690,7 +14663,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Tuyến Kênh Hữu Hòa</t>
@@ -14713,7 +14685,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Tuyến Kênh Hữu Hòa</t>
@@ -14736,7 +14707,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Tuyến Kênh Hữu Hòa</t>
@@ -14759,7 +14729,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14782,7 +14751,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14805,7 +14773,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14828,7 +14795,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14851,7 +14817,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14874,7 +14839,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14897,7 +14861,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14920,7 +14883,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14943,7 +14905,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14966,7 +14927,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -14989,7 +14949,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>Tuyến Kênh Tiêu Siêu Quần</t>
@@ -15012,7 +14971,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15035,7 +14993,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15058,7 +15015,6 @@
           <t>6 cửa</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15081,7 +15037,6 @@
           <t>6 cửa</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15104,7 +15059,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15127,7 +15081,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15150,7 +15103,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15173,7 +15125,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15196,7 +15147,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15219,7 +15169,6 @@
           <t>2 cánh</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15242,7 +15191,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15265,7 +15213,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15288,7 +15235,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15311,7 +15257,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15334,7 +15279,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15357,7 +15301,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15380,7 +15323,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15403,7 +15345,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15426,7 +15367,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15449,7 +15389,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15472,7 +15411,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15495,7 +15433,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15518,7 +15455,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15541,7 +15477,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>Tuyến Sông Hòa Bình</t>
@@ -15564,7 +15499,6 @@
           <t>3 cửa</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15587,7 +15521,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15610,7 +15543,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15633,7 +15565,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15656,7 +15587,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15679,7 +15609,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15702,7 +15631,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15725,7 +15653,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15748,7 +15675,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15771,7 +15697,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15794,7 +15719,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15817,7 +15741,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15840,7 +15763,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>Tuyến Sông Tô Lịch</t>
@@ -15863,7 +15785,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -15886,7 +15807,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -15909,7 +15829,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -15932,7 +15851,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -15955,7 +15873,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -15978,7 +15895,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -16001,7 +15917,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>Tuyến Vĩnh Quỳnh - Tả Thanh Oai</t>
@@ -16024,7 +15939,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16047,7 +15961,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16070,7 +15983,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16093,7 +16005,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16116,7 +16027,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16139,7 +16049,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16162,7 +16071,6 @@
           <t>2 cửa</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16185,7 +16093,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16208,7 +16115,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16231,7 +16137,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16254,7 +16159,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
@@ -16277,7 +16181,6 @@
           <t>1 cửa</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>Tuyến Đồng Trì - Đông Mỹ</t>
